--- a/data/Escenarios_DCH_agosto/Costo_variable/Swap_variable_3estaciones_160kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH_agosto/Costo_variable/Swap_variable_3estaciones_160kW/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_agosto\Costo_variable\Swap_variable_3estaciones_160kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4CCA94-8821-4F4D-9169-0AA8ED5AF3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC85C42-89BB-401B-B614-815BDBC193B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -3578,7 +3578,7 @@
         <v>38221</v>
       </c>
       <c r="E3">
-        <v>16725</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>5733</v>
@@ -3613,7 +3613,7 @@
         <v>38221</v>
       </c>
       <c r="E4">
-        <v>16725</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>5733</v>
@@ -3648,7 +3648,7 @@
         <v>38221</v>
       </c>
       <c r="E5">
-        <v>16725</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>5733</v>
